--- a/product_upload/packages/45/file.xlsx
+++ b/product_upload/packages/45/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -844,6 +849,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>Ascenta</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-FF826234CA25</t>
         </is>
       </c>
@@ -867,7 +877,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1042,6 +1052,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>Ascenta</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-C07EC476A55A</t>
         </is>
       </c>
@@ -1065,7 +1080,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1240,6 +1255,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>Vdia</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-79E93374E577</t>
         </is>
       </c>
@@ -1263,7 +1283,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1438,6 +1458,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>Vdia</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-D7D2B6B75F5D</t>
         </is>
       </c>
@@ -1461,7 +1486,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1624,6 +1649,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>Diva</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-5F2CC0DF783C</t>
         </is>
       </c>
@@ -1647,7 +1677,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1818,6 +1848,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>Slinda</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-CAB4415FE6BA</t>
         </is>
       </c>
@@ -1841,7 +1876,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2012,6 +2047,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>Exitor</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-09408B56B85D</t>
         </is>
       </c>
@@ -2035,7 +2075,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2206,6 +2246,11 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>Exitor</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-05F9CA38C843</t>
         </is>
       </c>
@@ -2229,7 +2274,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2396,6 +2441,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>Exitor</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-1AFB920F59D4</t>
         </is>
       </c>
@@ -2419,7 +2469,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2598,6 +2648,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>Tadil</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-656DF3B2BCFF</t>
         </is>
       </c>
@@ -2621,7 +2676,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2800,6 +2855,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>Tadil</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-B80EA1583015</t>
         </is>
       </c>
@@ -2823,7 +2883,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2994,6 +3054,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>Tadil</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-1D4D1A04E50E</t>
         </is>
       </c>
@@ -3017,7 +3082,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3184,6 +3249,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>Virtra</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-B801B6ECEB7A</t>
         </is>
       </c>
@@ -3207,7 +3277,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3386,6 +3456,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>ARGENTA</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-8C94D698927F</t>
         </is>
       </c>
@@ -3409,7 +3484,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3584,6 +3659,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>ARGENTA</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-E1D21BD72920</t>
         </is>
       </c>
@@ -3607,7 +3687,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3782,6 +3862,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>ARGENTA</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-BEE88A22BB89</t>
         </is>
       </c>
@@ -3805,7 +3890,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3974,6 +4059,11 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>Zorta</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-D427BF4995E0</t>
         </is>
       </c>
@@ -3997,7 +4087,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4164,6 +4254,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>Zorta</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-342A25DB2043</t>
         </is>
       </c>
@@ -4187,7 +4282,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4358,6 +4453,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>Rexofil</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-C3ABAA151EBC</t>
         </is>
       </c>
@@ -4381,7 +4481,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4548,6 +4648,11 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>Rexofil</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-84FF818ED6F9</t>
         </is>
       </c>
@@ -4571,7 +4676,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4734,6 +4839,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>Penetro</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-529993D47929</t>
         </is>
       </c>
@@ -4757,7 +4867,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4936,6 +5046,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>Blum-D</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-3ABE4DE4BD10</t>
         </is>
       </c>
@@ -4959,7 +5074,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5128,6 +5243,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>Parinso</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-C07F1D20C08E</t>
         </is>
       </c>
@@ -5151,7 +5271,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5324,6 +5444,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>Parinso</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-C4CA2FAF5908</t>
         </is>
       </c>
@@ -5347,7 +5472,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5516,6 +5641,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>Parinso</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-AC93158C8094</t>
         </is>
       </c>
@@ -5539,7 +5669,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5716,6 +5846,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>Parinso</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-1ACF8DF42BD3</t>
         </is>
       </c>
@@ -5739,7 +5874,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5908,6 +6043,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>FEXOFIN</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-3515C7FE4234</t>
         </is>
       </c>
@@ -5931,7 +6071,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -6096,6 +6236,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>Exdure</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-46903701BEA7</t>
         </is>
       </c>
@@ -6119,7 +6264,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6284,6 +6429,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>Exdure</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-9A5D0C00FAE3</t>
         </is>
       </c>
@@ -6307,7 +6457,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6472,6 +6622,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>Erastapecs Trio</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-2DCCECDA570E</t>
         </is>
       </c>
@@ -6495,7 +6650,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6660,6 +6815,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>Erastapecs Trio</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-CB7359F1B179</t>
         </is>
       </c>
@@ -6683,7 +6843,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6844,6 +7004,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>Erastapecs Trio</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-EBF7DBEF08CC</t>
         </is>
       </c>
@@ -6867,7 +7032,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -7038,6 +7203,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>XEVANEER 125mg/5ml Powder For Oral Suspension</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-A67BE035A650</t>
         </is>
       </c>
@@ -7061,7 +7231,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7224,6 +7394,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>Xivar</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-42B800733E20</t>
         </is>
       </c>
@@ -7247,7 +7422,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7410,6 +7585,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>Xivar</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-88DED98DC777</t>
         </is>
       </c>
@@ -7433,7 +7613,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7592,6 +7772,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>Xivar</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-A824C5800BEC</t>
         </is>
       </c>
@@ -7615,7 +7800,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KOREA</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7782,6 +7967,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>CLASGEN</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-832A1E541EF6</t>
         </is>
       </c>
@@ -7805,7 +7995,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7966,6 +8156,11 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>EPILYRE</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-09035F9574F1</t>
         </is>
       </c>
@@ -7989,7 +8184,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8150,6 +8345,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>EPILYRE</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-293F508E1D08</t>
         </is>
       </c>
@@ -8173,7 +8373,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8346,6 +8546,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>EXAMIDE</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-8A2D09578D8C</t>
         </is>
       </c>
@@ -8369,7 +8574,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8534,6 +8739,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>EXAMIDE</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-727B89DF9C59</t>
         </is>
       </c>
@@ -8557,7 +8767,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8730,6 +8940,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>EXAMIDE</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-EE3812775C89</t>
         </is>
       </c>
@@ -8753,7 +8968,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8928,6 +9143,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>CONTRAVE</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-DAC4C40CE91A</t>
         </is>
       </c>
@@ -8951,7 +9171,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -9118,6 +9338,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>GARDIA</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-F7E72E526909</t>
         </is>
       </c>
@@ -9141,7 +9366,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9300,6 +9525,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>FOLICUM</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-794DCF3C3BC7</t>
         </is>
       </c>
@@ -9323,7 +9553,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9486,6 +9716,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>FOLICUM</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-E7E1024A44CB</t>
         </is>
       </c>
@@ -9509,7 +9744,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9684,6 +9919,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>MAVENCLAD</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-BFFC6B5F4313</t>
         </is>
       </c>
@@ -9707,7 +9947,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9866,6 +10106,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>LEVOACT</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-420DE7E74A04</t>
         </is>
       </c>
@@ -9889,7 +10134,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -10048,6 +10293,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>AVIZOR LACRIFRESH OCU DRY 0.3%</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-B8FA34167139</t>
         </is>
       </c>
@@ -10071,7 +10321,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10246,6 +10496,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>Vyndamax</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-61093E4EBBC3</t>
         </is>
       </c>
@@ -10269,7 +10524,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10436,6 +10691,11 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>Minims Povidone Iodine 5%</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-3AD93DEAB713</t>
         </is>
       </c>
@@ -10459,7 +10719,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10622,6 +10882,11 @@
       </c>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>LEVOACT</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-9FE343FCBE84</t>
         </is>
       </c>
@@ -10645,7 +10910,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10816,6 +11081,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>Merional HG</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-04C1F5154A16</t>
         </is>
       </c>
@@ -10839,7 +11109,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -11014,6 +11284,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>MERIONAL HG</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-EC55E0BEAE2D</t>
         </is>
       </c>
@@ -11037,7 +11312,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11214,6 +11489,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>ABILIRAZOLE</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-471407501F88</t>
         </is>
       </c>
@@ -11237,7 +11517,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11414,6 +11694,11 @@
       </c>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>ABILIRAZOLE</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-D7A886672023</t>
         </is>
       </c>
@@ -11437,7 +11722,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11604,6 +11889,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>TECABEN</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-FA5C47953E26</t>
         </is>
       </c>
@@ -11627,7 +11917,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11794,6 +12084,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>TECABEN</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-B8F415AC21DF</t>
         </is>
       </c>
@@ -11817,7 +12112,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11990,6 +12285,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>OLMAZIDE 20/12.5MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-B6D7190A260A</t>
         </is>
       </c>
@@ -12013,7 +12313,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12190,6 +12490,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>OLMAZIDE 40/12.5MG</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-6975D37B3126</t>
         </is>
       </c>
@@ -12213,7 +12518,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12386,6 +12691,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>OLMAZIDE 40/25MG</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-C6B550E0AB12</t>
         </is>
       </c>
@@ -12409,7 +12719,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12582,6 +12892,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>DARINE</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-81CA874E97C9</t>
         </is>
       </c>
@@ -12605,7 +12920,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12780,6 +13095,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>OXIRA RAPID</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-526D3FB78932</t>
         </is>
       </c>
@@ -12803,7 +13123,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12962,6 +13282,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>LEVOACT</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-77FEDB1C6342</t>
         </is>
       </c>
@@ -12985,7 +13310,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -13136,6 +13461,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>Hyalfid Gel</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-5392319B3DC1</t>
         </is>
       </c>
@@ -13159,7 +13489,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13314,6 +13644,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>Hyalfid</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-8E4749E85993</t>
         </is>
       </c>
@@ -13337,7 +13672,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13508,6 +13843,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>CARELIO</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-F054D06860DC</t>
         </is>
       </c>
@@ -13531,7 +13871,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13706,6 +14046,11 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>CARELIO</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-7BE9E5E75270</t>
         </is>
       </c>
@@ -13729,7 +14074,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13900,6 +14245,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>CARELIO</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-29B575745029</t>
         </is>
       </c>
@@ -13923,7 +14273,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -14094,6 +14444,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>CARELIO</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-A005AC4F73C6</t>
         </is>
       </c>
@@ -14117,7 +14472,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14284,6 +14639,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>SPIOLTO RESPIMAT</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-D6095A921F44</t>
         </is>
       </c>
@@ -14307,7 +14667,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14478,6 +14838,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>HEMADID</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-A11ECD560B85</t>
         </is>
       </c>
@@ -14501,7 +14866,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14672,6 +15037,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>DABITRAN</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-9BEAC0CBDB27</t>
         </is>
       </c>
@@ -14695,7 +15065,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14866,6 +15236,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>DABITRAN</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-7DDD6E53CC4C</t>
         </is>
       </c>
@@ -14889,7 +15264,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -15056,6 +15431,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>DABITRAN</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-68CDFBE1EE13</t>
         </is>
       </c>
@@ -15079,7 +15459,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15254,6 +15634,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>DABITRAN</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-BED8E826DEA2</t>
         </is>
       </c>
@@ -15277,7 +15662,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15444,6 +15829,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>BIKTARVY</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-E5824D6436DF</t>
         </is>
       </c>
@@ -15467,7 +15857,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15636,6 +16026,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t xml:space="preserve"> Lamotrine</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-77DC526AC4E4</t>
         </is>
       </c>
@@ -15659,7 +16054,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15820,6 +16215,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>Lamotrine</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-D69F6B62B331</t>
         </is>
       </c>
@@ -15843,7 +16243,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -16008,6 +16408,11 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>Lamotrine</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-2EBD94D7C945</t>
         </is>
       </c>
@@ -16031,7 +16436,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16192,6 +16597,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>FONTAX</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-74563C3BCF54</t>
         </is>
       </c>
@@ -16215,7 +16625,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16378,6 +16788,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>Baxdela</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-0B4F0F4AFEBB</t>
         </is>
       </c>
@@ -16401,7 +16816,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16564,6 +16979,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>Loradin</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-16BC0319AA4D</t>
         </is>
       </c>
@@ -16587,7 +17007,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16762,6 +17182,11 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>Herptrex</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-EDFA45C6C23C</t>
         </is>
       </c>
@@ -16785,7 +17210,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16960,6 +17385,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>Herptrex</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-470C95E66AD6</t>
         </is>
       </c>
@@ -16983,7 +17413,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -17158,6 +17588,11 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>Bivoneb</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-302FBD4A7EFE</t>
         </is>
       </c>
@@ -17181,7 +17616,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17352,6 +17787,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>Vittoria</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-3D6CF0B7866A</t>
         </is>
       </c>
@@ -17375,7 +17815,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17542,6 +17982,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>Vittoria</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-8511303F8689</t>
         </is>
       </c>
@@ -17565,7 +18010,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17732,6 +18177,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>Vittoria</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-6319A41597F4</t>
         </is>
       </c>
@@ -17755,7 +18205,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17926,6 +18376,11 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>Vittoria</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-EBE8F34F8A91</t>
         </is>
       </c>
@@ -17949,7 +18404,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -18120,6 +18575,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t xml:space="preserve">Vildus </t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-A4C65C8454F0</t>
         </is>
       </c>
@@ -18143,7 +18603,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18314,6 +18774,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>Vildus</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-A3EC1651DE2D</t>
         </is>
       </c>
@@ -18337,7 +18802,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18496,6 +18961,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Keta </t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-DB51BC801FFC</t>
         </is>
       </c>
@@ -18519,7 +18989,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18678,6 +19148,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>Etvab</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-13C62C07A7FD</t>
         </is>
       </c>
@@ -18701,7 +19176,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18864,6 +19339,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>Etvab</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-18832B5B2A4F</t>
         </is>
       </c>
@@ -18887,7 +19367,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -19056,6 +19536,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>Enoxaparin BOS</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-95FC413C5460</t>
         </is>
       </c>
@@ -19079,7 +19564,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19244,6 +19729,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>Enoxaparin BOS</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-DD28FFC23BDB</t>
         </is>
       </c>
@@ -19267,7 +19757,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19432,6 +19922,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>Enoxaparin BOS</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-0FA44A08E59C</t>
         </is>
       </c>
@@ -19455,7 +19950,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19620,6 +20115,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>Enoxaparin BOS</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-3528C62A825B</t>
         </is>
       </c>
@@ -19643,7 +20143,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19805,6 +20305,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>Ribex</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-265203C6F0DF</t>
         </is>
@@ -19821,7 +20326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19867,100 +20372,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19992,7 +20502,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -20007,92 +20517,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-98046</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>214.78</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>419</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20124,7 +20639,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -20139,92 +20654,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-11188</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>97.29000000000001</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>420</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20256,7 +20776,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20271,92 +20791,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-60733</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>158.71</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>421</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20388,7 +20913,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20403,92 +20928,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-13481</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>465.47</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>422</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20520,7 +21050,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20535,92 +21065,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-11987</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>307.23</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>423</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20652,7 +21187,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20667,92 +21202,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-57662</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>300.71</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>424</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20784,7 +21324,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20799,92 +21339,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-68516</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>358.54</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>425</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20916,7 +21461,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20931,92 +21476,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-65782</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>82.2</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>426</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21048,7 +21598,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -21063,92 +21613,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-79378</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>491.75</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>427</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21180,7 +21735,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -21195,92 +21750,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-82841</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>150.6</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>428</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21312,7 +21872,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21327,92 +21887,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-88638</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>397.76</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>429</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21429,7 +21994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21535,6 +22100,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21570,7 +22145,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21635,6 +22210,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-156785D2489A</t>
         </is>
@@ -21671,7 +22256,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21736,6 +22321,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-1866B3920863</t>
         </is>
@@ -21772,7 +22367,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21837,6 +22432,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-E5B3ABA43AE1</t>
         </is>
@@ -21873,7 +22478,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21938,6 +22543,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-23BC59FA7DB2</t>
         </is>
@@ -21974,7 +22589,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -22039,6 +22654,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-22A6CA5FE2D0</t>
         </is>
@@ -22075,7 +22700,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -22140,6 +22765,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-ACAC6619701E</t>
         </is>
@@ -22176,7 +22811,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22241,6 +22876,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-4AC20B0C2E32</t>
         </is>
@@ -22277,7 +22922,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22342,6 +22987,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-FCF355651B1F</t>
         </is>
@@ -22378,7 +23033,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22443,6 +23098,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-CCBA8EFC933A</t>
         </is>
@@ -22479,7 +23144,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22544,6 +23209,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-765A6502C9CF</t>
         </is>
@@ -22580,7 +23255,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22645,6 +23320,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-B10A2A92EAAA</t>
         </is>
@@ -22681,7 +23366,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22746,6 +23431,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-C580B660F17A</t>
         </is>
@@ -22782,7 +23477,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22847,6 +23542,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-256D53FB7F40</t>
         </is>
@@ -22883,7 +23588,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22948,6 +23653,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-E4F061000A3A</t>
         </is>
@@ -22984,7 +23699,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -23049,6 +23764,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-02E82ECE4EE3</t>
         </is>
@@ -23085,7 +23810,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -23150,6 +23875,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-CABA3C050577</t>
         </is>
@@ -23186,7 +23921,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23251,6 +23986,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-BF6A280DB4A3</t>
         </is>
@@ -23287,7 +24032,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23352,6 +24097,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-3C9078D033AA</t>
         </is>
@@ -23388,7 +24143,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23453,6 +24208,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-A4AAF58518C3</t>
         </is>
@@ -23489,7 +24254,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23554,6 +24319,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-D9BBD93D581C</t>
         </is>

--- a/product_upload/packages/45/file.xlsx
+++ b/product_upload/packages/45/file.xlsx
@@ -686,8 +686,16 @@
           <t>4017851074-759-984979563058</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ascenta</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ascenta detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -1494,8 +1502,16 @@
           <t>2176111977-756-965987670162</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Diva</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Diva detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1884,8 +1900,16 @@
           <t>7348050956-201-334173509427</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Exitor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Exitor detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2083,8 +2107,16 @@
           <t>1344133713-543-146333002250</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Exitor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Exitor detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2282,8 +2314,16 @@
           <t>7776605603-924-648171995104</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Exitor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Exitor detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2891,8 +2931,16 @@
           <t>8396696975-620-036372556376</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tadil</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Tadil detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3090,8 +3138,16 @@
           <t>3921697917-433-618332933154</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Virtra</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Virtra detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3898,8 +3954,16 @@
           <t>4469779356-204-373917854742</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zorta</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Zorta detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -4095,8 +4159,16 @@
           <t>0791782601-001-850594173004</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zorta</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Zorta detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4489,8 +4561,16 @@
           <t>0272419508-408-380505488393</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rexofil</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Rexofil detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4684,8 +4764,16 @@
           <t>3957668726-931-759576264121</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Penetro</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Penetro detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -6079,8 +6167,16 @@
           <t>6883941923-604-587347254499</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Exdure</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Exdure detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -6272,8 +6368,16 @@
           <t>8877562635-378-352279603090</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Exdure</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Exdure detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -6465,8 +6569,16 @@
           <t>1935986419-711-757800372220</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Erastapecs Trio</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Erastapecs Trio detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -6658,8 +6770,16 @@
           <t>8267881974-774-218225263904</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Erastapecs Trio</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Erastapecs Trio detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -6851,8 +6971,16 @@
           <t>5240058583-872-833117803488</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Erastapecs Trio</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Erastapecs Trio detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -7239,8 +7367,16 @@
           <t>2909341655-498-503563495492</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Xivar</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Xivar detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7430,8 +7566,16 @@
           <t>8545092716-576-474205070536</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Xivar</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Xivar detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7621,8 +7765,16 @@
           <t>0100005651-168-041188952332</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Xivar</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Xivar detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -8003,8 +8155,16 @@
           <t>5869010609-782-261737294516</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EPILYRE</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>EPILYRE detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -8192,8 +8352,16 @@
           <t>3433134164-482-526559309212</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ EPILYRE</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>EPILYRE detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -9374,8 +9542,16 @@
           <t>6743953262-386-874567890827</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FOLICUM</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>FOLICUM detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9561,8 +9737,16 @@
           <t>4669232247-094-477345046212</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FOLICUM</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>FOLICUM detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9955,8 +10139,16 @@
           <t>6878274593-617-574153840934</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEVOACT</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>LEVOACT detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -10142,8 +10334,16 @@
           <t>7550294474-875-926625801525</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVIZOR LACRIFRESH OCU DRY 0.3%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>AVIZOR LACRIFRESH OCU DRY 0.3% detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -10532,8 +10732,16 @@
           <t>3752190001-901-541312804231</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Minims Povidone Iodine 5%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Minims Povidone Iodine 5% detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10727,8 +10935,16 @@
           <t>3107901176-639-680451702140</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEVOACT</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>LEVOACT detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -11730,8 +11946,16 @@
           <t>9415043679-960-113274939755</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TECABEN</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>TECABEN detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -13131,8 +13355,16 @@
           <t>4614297304-957-895541467566</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEVOACT</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>LEVOACT detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -13318,8 +13550,16 @@
           <t>0363971857-425-771594230248</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Hyalfid Gel</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Hyalfid Gel detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13497,8 +13737,16 @@
           <t>1574857476-994-177956466564</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Hyalfid</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Hyalfid detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -14480,8 +14728,16 @@
           <t>2060156548-615-601307713985</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SPIOLTO RESPIMAT</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>SPIOLTO RESPIMAT detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -15670,8 +15926,16 @@
           <t>3613578073-763-133234020274</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BIKTARVY</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>BIKTARVY detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -16062,8 +16326,16 @@
           <t>5021271324-773-505812111259</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lamotrine</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Lamotrine detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -16251,8 +16523,16 @@
           <t>7400343235-644-148848689162</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lamotrine</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Lamotrine detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -16444,8 +16724,16 @@
           <t>4345683188-547-124690858919</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FONTAX</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>FONTAX detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -16633,8 +16921,16 @@
           <t>7798312734-681-218005610782</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Baxdela</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Baxdela detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16824,8 +17120,16 @@
           <t>7540224820-632-833405827873</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Loradin</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Loradin detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -18810,8 +19114,16 @@
           <t>9370839601-758-078501269179</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Keta</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Keta detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18997,8 +19309,16 @@
           <t>3040193266-027-367709748306</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Etvab</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Etvab detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -19184,8 +19504,16 @@
           <t>3762890564-501-342495633723</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Etvab</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Etvab detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -19375,8 +19703,16 @@
           <t>5561104193-032-504265284198</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Enoxaparin BOS</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Enoxaparin BOS detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -19572,8 +19908,16 @@
           <t>5931695383-695-789522083295</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Enoxaparin BOS</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Enoxaparin BOS detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -19765,8 +20109,16 @@
           <t>8329957927-863-265566539451</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Enoxaparin BOS</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Enoxaparin BOS detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -19958,8 +20310,16 @@
           <t>2071777913-004-429488330066</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Enoxaparin BOS</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Enoxaparin BOS detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -20151,8 +20511,16 @@
           <t>8537196370-312-718365961018</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ribex</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Ribex detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/45/file.xlsx
+++ b/product_upload/packages/45/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22362,7 +22362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22443,40 +22443,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22556,38 +22561,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>487.69</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-156785D2489A</t>
         </is>
@@ -22667,38 +22677,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>314.62</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-1866B3920863</t>
         </is>
@@ -22778,38 +22793,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>109.81</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-E5B3ABA43AE1</t>
         </is>
@@ -22889,38 +22909,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>147.47</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-23BC59FA7DB2</t>
         </is>
@@ -23000,38 +23025,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>136.83</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-22A6CA5FE2D0</t>
         </is>
@@ -23111,38 +23141,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>396.05</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-ACAC6619701E</t>
         </is>
@@ -23222,38 +23257,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>325.24</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-4AC20B0C2E32</t>
         </is>
@@ -23333,38 +23373,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>245.54</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-FCF355651B1F</t>
         </is>
@@ -23444,38 +23489,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>368.79</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-CCBA8EFC933A</t>
         </is>
@@ -23555,38 +23605,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>472.05</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-765A6502C9CF</t>
         </is>
@@ -23666,38 +23721,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>180.2</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-B10A2A92EAAA</t>
         </is>
@@ -23777,38 +23837,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>305.68</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-C580B660F17A</t>
         </is>
@@ -23888,38 +23953,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>264.1</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-256D53FB7F40</t>
         </is>
@@ -23999,38 +24069,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>217.37</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-E4F061000A3A</t>
         </is>
@@ -24110,38 +24185,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>259.22</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-02E82ECE4EE3</t>
         </is>
@@ -24221,38 +24301,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>232.97</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-CABA3C050577</t>
         </is>
@@ -24332,38 +24417,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>56.98</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-BF6A280DB4A3</t>
         </is>
@@ -24443,38 +24533,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>337.14</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-3C9078D033AA</t>
         </is>
@@ -24554,38 +24649,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>13.37</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-A4AAF58518C3</t>
         </is>
@@ -24665,38 +24765,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>337.58</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-D9BBD93D581C</t>
         </is>
